--- a/config/knowledge_base/knowledge_base.xlsx
+++ b/config/knowledge_base/knowledge_base.xlsx
@@ -1,13 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JetBrains\cl_mail_assistant_mooon\config\knowledge_base\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECA326F2-C004-489E-9867-7025D8CA42CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="KB_ITEMS" sheetId="1" r:id="rId1"/>
+    <sheet name="KB_DICTIONARY" sheetId="2" r:id="rId2"/>
+    <sheet name="KB_TYPES" sheetId="3" r:id="rId3"/>
+    <sheet name="KB_SETTINGS" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -19,7 +28,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -53,7 +62,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,9 +339,36 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D2CB978-864B-41A6-82AC-FC142A4E17A9}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62CDAD6A-3E58-44ED-881F-FD70CCFD0F42}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA296E6B-AA0E-474A-BDE2-31CF86C0819A}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/knowledge_base/knowledge_base.xlsx
+++ b/config/knowledge_base/knowledge_base.xlsx
@@ -2,10 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KB_ITEMS" sheetId="1" r:id="Rb3bacd7fcac649da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KB_DICTIONARY" sheetId="2" r:id="R22aa41f7e37a4f8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KB_TYPES" sheetId="3" r:id="R2f9c9bb415dd4daa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KB_SETTINGS" sheetId="4" r:id="R6c2af10608b24a34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KB_ITEMS" sheetId="1" r:id="R37cff0c29460465a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KB_DICTIONARY" sheetId="2" r:id="Rebbb59401afa4004"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KB_TYPES" sheetId="3" r:id="R38720bd3da1a4ef3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KB_SETTINGS" sheetId="4" r:id="Ra1b4814a4ff2450f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KB_ROUTING" sheetId="5" r:id="R3e8ef866c03841a5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -28,12 +29,17 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="1F2937"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -48,7 +54,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="22">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -85,6 +91,18 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -95,7 +113,7 @@
         <x:color rgb="6B7280"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="E5E7EB"/>
         </x:patternFill>
       </x:fill>
@@ -4926,7 +4944,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c97325b66114686"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd300afa634f3427f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5472,7 +5490,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5fae61396206482f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdec3f688f43c443b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5566,7 +5584,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c911643155a40d9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a4f24dc5d724311"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5701,10 +5719,746 @@
         <x:v>Дата сборки этой версии workbook.</x:v>
       </x:c>
     </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="12" t="str">
+        <x:v>max_routing_results</x:v>
+      </x:c>
+      <x:c r="B12" s="12" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C12" s="12" t="str">
+        <x:v>Максимальное количество найденных маршрутов из листа KB_ROUTING.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="12" t="str">
+        <x:v>routing_source</x:v>
+      </x:c>
+      <x:c r="B13" s="12" t="str">
+        <x:v>KB_ROUTING</x:v>
+      </x:c>
+      <x:c r="C13" s="12" t="str">
+        <x:v>Справочник отделов и email для рекомендации передачи обращения.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8fdcdd3a710440d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R959147b655974a0a"/>
   </x:tableParts>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="30" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="34" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="58" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="70" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="26" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="10" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="58" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="21" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="B1" s="21" t="str">
+        <x:v>enabled</x:v>
+      </x:c>
+      <x:c r="C1" s="21" t="str">
+        <x:v>department</x:v>
+      </x:c>
+      <x:c r="D1" s="21" t="str">
+        <x:v>contact_name</x:v>
+      </x:c>
+      <x:c r="E1" s="21" t="str">
+        <x:v>email</x:v>
+      </x:c>
+      <x:c r="F1" s="21" t="str">
+        <x:v>title</x:v>
+      </x:c>
+      <x:c r="G1" s="21" t="str">
+        <x:v>description</x:v>
+      </x:c>
+      <x:c r="H1" s="21" t="str">
+        <x:v>keywords</x:v>
+      </x:c>
+      <x:c r="I1" s="21" t="str">
+        <x:v>applies_to</x:v>
+      </x:c>
+      <x:c r="J1" s="21" t="str">
+        <x:v>priority</x:v>
+      </x:c>
+      <x:c r="K1" s="21" t="str">
+        <x:v>notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="12" t="str">
+        <x:v>route_marketing</x:v>
+      </x:c>
+      <x:c r="B2" s="12" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="C2" s="12" t="str">
+        <x:v>Маркетинг</x:v>
+      </x:c>
+      <x:c r="D2" s="12" t="str"/>
+      <x:c r="E2" s="12" t="str">
+        <x:v>marketing@mooon.by</x:v>
+      </x:c>
+      <x:c r="F2" s="12" t="str">
+        <x:v>Маркетинг / реклама / партнерства</x:v>
+      </x:c>
+      <x:c r="G2" s="12" t="str">
+        <x:v>Вопросы рекламы, маркетинга, партнерств, продвижения, коллабораций, промо-размещений и спецпроектов.</x:v>
+      </x:c>
+      <x:c r="H2" s="12" t="str">
+        <x:v>маркетинг; реклама; рекламное; рекламная; рекламные; партнерство; партнёрство; партнерства; партнёрства; продвижение; промо; коллаборация; коллаборации; медиапартнерство; интеграция; бартер; спецпроект; афиша; размещение</x:v>
+      </x:c>
+      <x:c r="I2" s="12" t="str">
+        <x:v>partner; counterparty; customer</x:v>
+      </x:c>
+      <x:c r="J2" s="12" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="K2" s="12" t="str">
+        <x:v>Управляется только через этот лист. В коде нет fallback-маршрутов.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="12"/>
+      <x:c r="B3" s="12"/>
+      <x:c r="C3" s="12"/>
+      <x:c r="D3" s="12"/>
+      <x:c r="E3" s="12"/>
+      <x:c r="F3" s="12"/>
+      <x:c r="G3" s="12"/>
+      <x:c r="H3" s="12"/>
+      <x:c r="I3" s="12"/>
+      <x:c r="J3" s="12"/>
+      <x:c r="K3" s="12"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="12"/>
+      <x:c r="B4" s="12"/>
+      <x:c r="C4" s="12"/>
+      <x:c r="D4" s="12"/>
+      <x:c r="E4" s="12"/>
+      <x:c r="F4" s="12"/>
+      <x:c r="G4" s="12"/>
+      <x:c r="H4" s="12"/>
+      <x:c r="I4" s="12"/>
+      <x:c r="J4" s="12"/>
+      <x:c r="K4" s="12"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="12"/>
+      <x:c r="B5" s="12"/>
+      <x:c r="C5" s="12"/>
+      <x:c r="D5" s="12"/>
+      <x:c r="E5" s="12"/>
+      <x:c r="F5" s="12"/>
+      <x:c r="G5" s="12"/>
+      <x:c r="H5" s="12"/>
+      <x:c r="I5" s="12"/>
+      <x:c r="J5" s="12"/>
+      <x:c r="K5" s="12"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="12"/>
+      <x:c r="B6" s="12"/>
+      <x:c r="C6" s="12"/>
+      <x:c r="D6" s="12"/>
+      <x:c r="E6" s="12"/>
+      <x:c r="F6" s="12"/>
+      <x:c r="G6" s="12"/>
+      <x:c r="H6" s="12"/>
+      <x:c r="I6" s="12"/>
+      <x:c r="J6" s="12"/>
+      <x:c r="K6" s="12"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="12"/>
+      <x:c r="B7" s="12"/>
+      <x:c r="C7" s="12"/>
+      <x:c r="D7" s="12"/>
+      <x:c r="E7" s="12"/>
+      <x:c r="F7" s="12"/>
+      <x:c r="G7" s="12"/>
+      <x:c r="H7" s="12"/>
+      <x:c r="I7" s="12"/>
+      <x:c r="J7" s="12"/>
+      <x:c r="K7" s="12"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="12"/>
+      <x:c r="B8" s="12"/>
+      <x:c r="C8" s="12"/>
+      <x:c r="D8" s="12"/>
+      <x:c r="E8" s="12"/>
+      <x:c r="F8" s="12"/>
+      <x:c r="G8" s="12"/>
+      <x:c r="H8" s="12"/>
+      <x:c r="I8" s="12"/>
+      <x:c r="J8" s="12"/>
+      <x:c r="K8" s="12"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="12"/>
+      <x:c r="B9" s="12"/>
+      <x:c r="C9" s="12"/>
+      <x:c r="D9" s="12"/>
+      <x:c r="E9" s="12"/>
+      <x:c r="F9" s="12"/>
+      <x:c r="G9" s="12"/>
+      <x:c r="H9" s="12"/>
+      <x:c r="I9" s="12"/>
+      <x:c r="J9" s="12"/>
+      <x:c r="K9" s="12"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="12"/>
+      <x:c r="B10" s="12"/>
+      <x:c r="C10" s="12"/>
+      <x:c r="D10" s="12"/>
+      <x:c r="E10" s="12"/>
+      <x:c r="F10" s="12"/>
+      <x:c r="G10" s="12"/>
+      <x:c r="H10" s="12"/>
+      <x:c r="I10" s="12"/>
+      <x:c r="J10" s="12"/>
+      <x:c r="K10" s="12"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="12"/>
+      <x:c r="B11" s="12"/>
+      <x:c r="C11" s="12"/>
+      <x:c r="D11" s="12"/>
+      <x:c r="E11" s="12"/>
+      <x:c r="F11" s="12"/>
+      <x:c r="G11" s="12"/>
+      <x:c r="H11" s="12"/>
+      <x:c r="I11" s="12"/>
+      <x:c r="J11" s="12"/>
+      <x:c r="K11" s="12"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="12"/>
+      <x:c r="B12" s="12"/>
+      <x:c r="C12" s="12"/>
+      <x:c r="D12" s="12"/>
+      <x:c r="E12" s="12"/>
+      <x:c r="F12" s="12"/>
+      <x:c r="G12" s="12"/>
+      <x:c r="H12" s="12"/>
+      <x:c r="I12" s="12"/>
+      <x:c r="J12" s="12"/>
+      <x:c r="K12" s="12"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="12"/>
+      <x:c r="B13" s="12"/>
+      <x:c r="C13" s="12"/>
+      <x:c r="D13" s="12"/>
+      <x:c r="E13" s="12"/>
+      <x:c r="F13" s="12"/>
+      <x:c r="G13" s="12"/>
+      <x:c r="H13" s="12"/>
+      <x:c r="I13" s="12"/>
+      <x:c r="J13" s="12"/>
+      <x:c r="K13" s="12"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="12"/>
+      <x:c r="B14" s="12"/>
+      <x:c r="C14" s="12"/>
+      <x:c r="D14" s="12"/>
+      <x:c r="E14" s="12"/>
+      <x:c r="F14" s="12"/>
+      <x:c r="G14" s="12"/>
+      <x:c r="H14" s="12"/>
+      <x:c r="I14" s="12"/>
+      <x:c r="J14" s="12"/>
+      <x:c r="K14" s="12"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="12"/>
+      <x:c r="B15" s="12"/>
+      <x:c r="C15" s="12"/>
+      <x:c r="D15" s="12"/>
+      <x:c r="E15" s="12"/>
+      <x:c r="F15" s="12"/>
+      <x:c r="G15" s="12"/>
+      <x:c r="H15" s="12"/>
+      <x:c r="I15" s="12"/>
+      <x:c r="J15" s="12"/>
+      <x:c r="K15" s="12"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="12"/>
+      <x:c r="B16" s="12"/>
+      <x:c r="C16" s="12"/>
+      <x:c r="D16" s="12"/>
+      <x:c r="E16" s="12"/>
+      <x:c r="F16" s="12"/>
+      <x:c r="G16" s="12"/>
+      <x:c r="H16" s="12"/>
+      <x:c r="I16" s="12"/>
+      <x:c r="J16" s="12"/>
+      <x:c r="K16" s="12"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="12"/>
+      <x:c r="B17" s="12"/>
+      <x:c r="C17" s="12"/>
+      <x:c r="D17" s="12"/>
+      <x:c r="E17" s="12"/>
+      <x:c r="F17" s="12"/>
+      <x:c r="G17" s="12"/>
+      <x:c r="H17" s="12"/>
+      <x:c r="I17" s="12"/>
+      <x:c r="J17" s="12"/>
+      <x:c r="K17" s="12"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="12"/>
+      <x:c r="B18" s="12"/>
+      <x:c r="C18" s="12"/>
+      <x:c r="D18" s="12"/>
+      <x:c r="E18" s="12"/>
+      <x:c r="F18" s="12"/>
+      <x:c r="G18" s="12"/>
+      <x:c r="H18" s="12"/>
+      <x:c r="I18" s="12"/>
+      <x:c r="J18" s="12"/>
+      <x:c r="K18" s="12"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="12"/>
+      <x:c r="B19" s="12"/>
+      <x:c r="C19" s="12"/>
+      <x:c r="D19" s="12"/>
+      <x:c r="E19" s="12"/>
+      <x:c r="F19" s="12"/>
+      <x:c r="G19" s="12"/>
+      <x:c r="H19" s="12"/>
+      <x:c r="I19" s="12"/>
+      <x:c r="J19" s="12"/>
+      <x:c r="K19" s="12"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="12"/>
+      <x:c r="B20" s="12"/>
+      <x:c r="C20" s="12"/>
+      <x:c r="D20" s="12"/>
+      <x:c r="E20" s="12"/>
+      <x:c r="F20" s="12"/>
+      <x:c r="G20" s="12"/>
+      <x:c r="H20" s="12"/>
+      <x:c r="I20" s="12"/>
+      <x:c r="J20" s="12"/>
+      <x:c r="K20" s="12"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="12"/>
+      <x:c r="B21" s="12"/>
+      <x:c r="C21" s="12"/>
+      <x:c r="D21" s="12"/>
+      <x:c r="E21" s="12"/>
+      <x:c r="F21" s="12"/>
+      <x:c r="G21" s="12"/>
+      <x:c r="H21" s="12"/>
+      <x:c r="I21" s="12"/>
+      <x:c r="J21" s="12"/>
+      <x:c r="K21" s="12"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="12"/>
+      <x:c r="B22" s="12"/>
+      <x:c r="C22" s="12"/>
+      <x:c r="D22" s="12"/>
+      <x:c r="E22" s="12"/>
+      <x:c r="F22" s="12"/>
+      <x:c r="G22" s="12"/>
+      <x:c r="H22" s="12"/>
+      <x:c r="I22" s="12"/>
+      <x:c r="J22" s="12"/>
+      <x:c r="K22" s="12"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="12"/>
+      <x:c r="B23" s="12"/>
+      <x:c r="C23" s="12"/>
+      <x:c r="D23" s="12"/>
+      <x:c r="E23" s="12"/>
+      <x:c r="F23" s="12"/>
+      <x:c r="G23" s="12"/>
+      <x:c r="H23" s="12"/>
+      <x:c r="I23" s="12"/>
+      <x:c r="J23" s="12"/>
+      <x:c r="K23" s="12"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="12"/>
+      <x:c r="B24" s="12"/>
+      <x:c r="C24" s="12"/>
+      <x:c r="D24" s="12"/>
+      <x:c r="E24" s="12"/>
+      <x:c r="F24" s="12"/>
+      <x:c r="G24" s="12"/>
+      <x:c r="H24" s="12"/>
+      <x:c r="I24" s="12"/>
+      <x:c r="J24" s="12"/>
+      <x:c r="K24" s="12"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="12"/>
+      <x:c r="B25" s="12"/>
+      <x:c r="C25" s="12"/>
+      <x:c r="D25" s="12"/>
+      <x:c r="E25" s="12"/>
+      <x:c r="F25" s="12"/>
+      <x:c r="G25" s="12"/>
+      <x:c r="H25" s="12"/>
+      <x:c r="I25" s="12"/>
+      <x:c r="J25" s="12"/>
+      <x:c r="K25" s="12"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="12"/>
+      <x:c r="B26" s="12"/>
+      <x:c r="C26" s="12"/>
+      <x:c r="D26" s="12"/>
+      <x:c r="E26" s="12"/>
+      <x:c r="F26" s="12"/>
+      <x:c r="G26" s="12"/>
+      <x:c r="H26" s="12"/>
+      <x:c r="I26" s="12"/>
+      <x:c r="J26" s="12"/>
+      <x:c r="K26" s="12"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="12"/>
+      <x:c r="B27" s="12"/>
+      <x:c r="C27" s="12"/>
+      <x:c r="D27" s="12"/>
+      <x:c r="E27" s="12"/>
+      <x:c r="F27" s="12"/>
+      <x:c r="G27" s="12"/>
+      <x:c r="H27" s="12"/>
+      <x:c r="I27" s="12"/>
+      <x:c r="J27" s="12"/>
+      <x:c r="K27" s="12"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="12"/>
+      <x:c r="B28" s="12"/>
+      <x:c r="C28" s="12"/>
+      <x:c r="D28" s="12"/>
+      <x:c r="E28" s="12"/>
+      <x:c r="F28" s="12"/>
+      <x:c r="G28" s="12"/>
+      <x:c r="H28" s="12"/>
+      <x:c r="I28" s="12"/>
+      <x:c r="J28" s="12"/>
+      <x:c r="K28" s="12"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="12"/>
+      <x:c r="B29" s="12"/>
+      <x:c r="C29" s="12"/>
+      <x:c r="D29" s="12"/>
+      <x:c r="E29" s="12"/>
+      <x:c r="F29" s="12"/>
+      <x:c r="G29" s="12"/>
+      <x:c r="H29" s="12"/>
+      <x:c r="I29" s="12"/>
+      <x:c r="J29" s="12"/>
+      <x:c r="K29" s="12"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="12"/>
+      <x:c r="B30" s="12"/>
+      <x:c r="C30" s="12"/>
+      <x:c r="D30" s="12"/>
+      <x:c r="E30" s="12"/>
+      <x:c r="F30" s="12"/>
+      <x:c r="G30" s="12"/>
+      <x:c r="H30" s="12"/>
+      <x:c r="I30" s="12"/>
+      <x:c r="J30" s="12"/>
+      <x:c r="K30" s="12"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="12"/>
+      <x:c r="B31" s="12"/>
+      <x:c r="C31" s="12"/>
+      <x:c r="D31" s="12"/>
+      <x:c r="E31" s="12"/>
+      <x:c r="F31" s="12"/>
+      <x:c r="G31" s="12"/>
+      <x:c r="H31" s="12"/>
+      <x:c r="I31" s="12"/>
+      <x:c r="J31" s="12"/>
+      <x:c r="K31" s="12"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="12"/>
+      <x:c r="B32" s="12"/>
+      <x:c r="C32" s="12"/>
+      <x:c r="D32" s="12"/>
+      <x:c r="E32" s="12"/>
+      <x:c r="F32" s="12"/>
+      <x:c r="G32" s="12"/>
+      <x:c r="H32" s="12"/>
+      <x:c r="I32" s="12"/>
+      <x:c r="J32" s="12"/>
+      <x:c r="K32" s="12"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="12"/>
+      <x:c r="B33" s="12"/>
+      <x:c r="C33" s="12"/>
+      <x:c r="D33" s="12"/>
+      <x:c r="E33" s="12"/>
+      <x:c r="F33" s="12"/>
+      <x:c r="G33" s="12"/>
+      <x:c r="H33" s="12"/>
+      <x:c r="I33" s="12"/>
+      <x:c r="J33" s="12"/>
+      <x:c r="K33" s="12"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="12"/>
+      <x:c r="B34" s="12"/>
+      <x:c r="C34" s="12"/>
+      <x:c r="D34" s="12"/>
+      <x:c r="E34" s="12"/>
+      <x:c r="F34" s="12"/>
+      <x:c r="G34" s="12"/>
+      <x:c r="H34" s="12"/>
+      <x:c r="I34" s="12"/>
+      <x:c r="J34" s="12"/>
+      <x:c r="K34" s="12"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="12"/>
+      <x:c r="B35" s="12"/>
+      <x:c r="C35" s="12"/>
+      <x:c r="D35" s="12"/>
+      <x:c r="E35" s="12"/>
+      <x:c r="F35" s="12"/>
+      <x:c r="G35" s="12"/>
+      <x:c r="H35" s="12"/>
+      <x:c r="I35" s="12"/>
+      <x:c r="J35" s="12"/>
+      <x:c r="K35" s="12"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="12"/>
+      <x:c r="B36" s="12"/>
+      <x:c r="C36" s="12"/>
+      <x:c r="D36" s="12"/>
+      <x:c r="E36" s="12"/>
+      <x:c r="F36" s="12"/>
+      <x:c r="G36" s="12"/>
+      <x:c r="H36" s="12"/>
+      <x:c r="I36" s="12"/>
+      <x:c r="J36" s="12"/>
+      <x:c r="K36" s="12"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="12"/>
+      <x:c r="B37" s="12"/>
+      <x:c r="C37" s="12"/>
+      <x:c r="D37" s="12"/>
+      <x:c r="E37" s="12"/>
+      <x:c r="F37" s="12"/>
+      <x:c r="G37" s="12"/>
+      <x:c r="H37" s="12"/>
+      <x:c r="I37" s="12"/>
+      <x:c r="J37" s="12"/>
+      <x:c r="K37" s="12"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="12"/>
+      <x:c r="B38" s="12"/>
+      <x:c r="C38" s="12"/>
+      <x:c r="D38" s="12"/>
+      <x:c r="E38" s="12"/>
+      <x:c r="F38" s="12"/>
+      <x:c r="G38" s="12"/>
+      <x:c r="H38" s="12"/>
+      <x:c r="I38" s="12"/>
+      <x:c r="J38" s="12"/>
+      <x:c r="K38" s="12"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="12"/>
+      <x:c r="B39" s="12"/>
+      <x:c r="C39" s="12"/>
+      <x:c r="D39" s="12"/>
+      <x:c r="E39" s="12"/>
+      <x:c r="F39" s="12"/>
+      <x:c r="G39" s="12"/>
+      <x:c r="H39" s="12"/>
+      <x:c r="I39" s="12"/>
+      <x:c r="J39" s="12"/>
+      <x:c r="K39" s="12"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="12"/>
+      <x:c r="B40" s="12"/>
+      <x:c r="C40" s="12"/>
+      <x:c r="D40" s="12"/>
+      <x:c r="E40" s="12"/>
+      <x:c r="F40" s="12"/>
+      <x:c r="G40" s="12"/>
+      <x:c r="H40" s="12"/>
+      <x:c r="I40" s="12"/>
+      <x:c r="J40" s="12"/>
+      <x:c r="K40" s="12"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="12"/>
+      <x:c r="B41" s="12"/>
+      <x:c r="C41" s="12"/>
+      <x:c r="D41" s="12"/>
+      <x:c r="E41" s="12"/>
+      <x:c r="F41" s="12"/>
+      <x:c r="G41" s="12"/>
+      <x:c r="H41" s="12"/>
+      <x:c r="I41" s="12"/>
+      <x:c r="J41" s="12"/>
+      <x:c r="K41" s="12"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="12"/>
+      <x:c r="B42" s="12"/>
+      <x:c r="C42" s="12"/>
+      <x:c r="D42" s="12"/>
+      <x:c r="E42" s="12"/>
+      <x:c r="F42" s="12"/>
+      <x:c r="G42" s="12"/>
+      <x:c r="H42" s="12"/>
+      <x:c r="I42" s="12"/>
+      <x:c r="J42" s="12"/>
+      <x:c r="K42" s="12"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="12"/>
+      <x:c r="B43" s="12"/>
+      <x:c r="C43" s="12"/>
+      <x:c r="D43" s="12"/>
+      <x:c r="E43" s="12"/>
+      <x:c r="F43" s="12"/>
+      <x:c r="G43" s="12"/>
+      <x:c r="H43" s="12"/>
+      <x:c r="I43" s="12"/>
+      <x:c r="J43" s="12"/>
+      <x:c r="K43" s="12"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="12"/>
+      <x:c r="B44" s="12"/>
+      <x:c r="C44" s="12"/>
+      <x:c r="D44" s="12"/>
+      <x:c r="E44" s="12"/>
+      <x:c r="F44" s="12"/>
+      <x:c r="G44" s="12"/>
+      <x:c r="H44" s="12"/>
+      <x:c r="I44" s="12"/>
+      <x:c r="J44" s="12"/>
+      <x:c r="K44" s="12"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="12"/>
+      <x:c r="B45" s="12"/>
+      <x:c r="C45" s="12"/>
+      <x:c r="D45" s="12"/>
+      <x:c r="E45" s="12"/>
+      <x:c r="F45" s="12"/>
+      <x:c r="G45" s="12"/>
+      <x:c r="H45" s="12"/>
+      <x:c r="I45" s="12"/>
+      <x:c r="J45" s="12"/>
+      <x:c r="K45" s="12"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="12"/>
+      <x:c r="B46" s="12"/>
+      <x:c r="C46" s="12"/>
+      <x:c r="D46" s="12"/>
+      <x:c r="E46" s="12"/>
+      <x:c r="F46" s="12"/>
+      <x:c r="G46" s="12"/>
+      <x:c r="H46" s="12"/>
+      <x:c r="I46" s="12"/>
+      <x:c r="J46" s="12"/>
+      <x:c r="K46" s="12"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="12"/>
+      <x:c r="B47" s="12"/>
+      <x:c r="C47" s="12"/>
+      <x:c r="D47" s="12"/>
+      <x:c r="E47" s="12"/>
+      <x:c r="F47" s="12"/>
+      <x:c r="G47" s="12"/>
+      <x:c r="H47" s="12"/>
+      <x:c r="I47" s="12"/>
+      <x:c r="J47" s="12"/>
+      <x:c r="K47" s="12"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="12"/>
+      <x:c r="B48" s="12"/>
+      <x:c r="C48" s="12"/>
+      <x:c r="D48" s="12"/>
+      <x:c r="E48" s="12"/>
+      <x:c r="F48" s="12"/>
+      <x:c r="G48" s="12"/>
+      <x:c r="H48" s="12"/>
+      <x:c r="I48" s="12"/>
+      <x:c r="J48" s="12"/>
+      <x:c r="K48" s="12"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="12"/>
+      <x:c r="B49" s="12"/>
+      <x:c r="C49" s="12"/>
+      <x:c r="D49" s="12"/>
+      <x:c r="E49" s="12"/>
+      <x:c r="F49" s="12"/>
+      <x:c r="G49" s="12"/>
+      <x:c r="H49" s="12"/>
+      <x:c r="I49" s="12"/>
+      <x:c r="J49" s="12"/>
+      <x:c r="K49" s="12"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="12"/>
+      <x:c r="B50" s="12"/>
+      <x:c r="C50" s="12"/>
+      <x:c r="D50" s="12"/>
+      <x:c r="E50" s="12"/>
+      <x:c r="F50" s="12"/>
+      <x:c r="G50" s="12"/>
+      <x:c r="H50" s="12"/>
+      <x:c r="I50" s="12"/>
+      <x:c r="J50" s="12"/>
+      <x:c r="K50" s="12"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>